--- a/outputs/chip-report/台股盤後籌碼_2026-08-19.xlsx
+++ b/outputs/chip-report/台股盤後籌碼_2026-08-19.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,11 +57,17 @@
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
+      <b val="1"/>
+      <color rgb="009f1239"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
       <color rgb="001f2d3d"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -113,6 +119,16 @@
         <fgColor rgb="00eef7e8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00fca5a5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00fff1f2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -140,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -185,7 +201,16 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -553,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N126"/>
+  <dimension ref="A1:N132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1725,12 +1750,12 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
-        <v>30371</v>
+        <v>23034</v>
       </c>
       <c r="B92" s="6" t="n"/>
       <c r="C92" s="6" t="n"/>
       <c r="E92" s="6" t="n">
-        <v>21407</v>
+        <v>14070</v>
       </c>
       <c r="F92" s="6" t="n"/>
       <c r="G92" s="6" t="n"/>
@@ -1754,14 +1779,14 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>MTX 全市場OI 34,223 - (自營1,714 + 投信109 + 外資2,029)</t>
+          <t>MTX 全市場OI 26,886 - (自營1,714 + 投信109 + 外資2,029)</t>
         </is>
       </c>
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>MTX 全市場OI 34,223 - (自營9,487 + 投信156 + 外資3,173)</t>
+          <t>MTX 全市場OI 26,886 - (自營9,487 + 投信156 + 外資3,173)</t>
         </is>
       </c>
       <c r="F94" s="7" t="n"/>
@@ -1816,12 +1841,12 @@
       <c r="B98" s="6" t="n"/>
       <c r="C98" s="6" t="n"/>
       <c r="E98" s="6" t="n">
-        <v>76319</v>
+        <v>58350</v>
       </c>
       <c r="F98" s="6" t="n"/>
       <c r="G98" s="6" t="n"/>
       <c r="I98" s="6" t="n">
-        <v>47270</v>
+        <v>29301</v>
       </c>
       <c r="J98" s="6" t="n"/>
       <c r="K98" s="6" t="n"/>
@@ -1840,21 +1865,21 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>30,371 - 21,407</t>
+          <t>23,034 - 14,070</t>
         </is>
       </c>
       <c r="B100" s="7" t="n"/>
       <c r="C100" s="7" t="n"/>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>TMF 全市場OI 79,929 - (自營2,898 + 投信0 + 外資712)</t>
+          <t>TMF 全市場OI 61,960 - (自營2,898 + 投信0 + 外資712)</t>
         </is>
       </c>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
       <c r="I100" s="7" t="inlineStr">
         <is>
-          <t>TMF 全市場OI 79,929 - (自營31,423 + 投信0 + 外資1,236)</t>
+          <t>TMF 全市場OI 61,960 - (自營31,423 + 投信0 + 外資1,236)</t>
         </is>
       </c>
       <c r="J100" s="7" t="n"/>
@@ -1896,7 +1921,7 @@
     </row>
     <row r="104">
       <c r="A104" s="6" t="n">
-        <v>36.34350486056375</v>
+        <v>46.88347320852163</v>
       </c>
       <c r="B104" s="6" t="n"/>
       <c r="C104" s="6" t="n"/>
@@ -1906,7 +1931,7 @@
       <c r="F104" s="6" t="n"/>
       <c r="G104" s="6" t="n"/>
       <c r="I104" s="6" t="n">
-        <v>45634.8</v>
+        <v>34704</v>
       </c>
       <c r="J104" s="6" t="n"/>
       <c r="K104" s="6" t="n"/>
@@ -1925,21 +1950,21 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>(29,049 / 79,929) x 100</t>
+          <t>(29,049 / 61,960) x 100</t>
         </is>
       </c>
       <c r="B106" s="7" t="n"/>
       <c r="C106" s="7" t="n"/>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>76,319 - 47,270</t>
+          <t>58,350 - 29,301</t>
         </is>
       </c>
       <c r="F106" s="7" t="n"/>
       <c r="G106" s="7" t="n"/>
       <c r="I106" s="7" t="inlineStr">
         <is>
-          <t>30,371 + 76,319 / 5；微台 5 口換算 1 口小台等值</t>
+          <t>23,034 + 58,350 / 5；微台 5 口換算 1 口小台等值</t>
         </is>
       </c>
       <c r="J106" s="7" t="n"/>
@@ -1981,7 +2006,7 @@
     </row>
     <row r="110">
       <c r="A110" s="6" t="n">
-        <v>30861</v>
+        <v>19930.2</v>
       </c>
       <c r="B110" s="6" t="n"/>
       <c r="C110" s="6" t="n"/>
@@ -1991,7 +2016,7 @@
       <c r="F110" s="6" t="n"/>
       <c r="G110" s="6" t="n"/>
       <c r="I110" s="6" t="n">
-        <v>43.3</v>
+        <v>1.1</v>
       </c>
       <c r="J110" s="6" t="n"/>
       <c r="K110" s="6" t="n"/>
@@ -2010,14 +2035,14 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>21,407 + 47,270 / 5；微台 5 口換算 1 口小台等值</t>
+          <t>14,070 + 29,301 / 5；微台 5 口換算 1 口小台等值</t>
         </is>
       </c>
       <c r="B112" s="7" t="n"/>
       <c r="C112" s="7" t="n"/>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>45,634.8 - 30,861.0</t>
+          <t>34,704.0 - 19,930.2</t>
         </is>
       </c>
       <c r="F112" s="7" t="n"/>
@@ -2056,17 +2081,18 @@
       </c>
       <c r="F115" s="15" t="n"/>
       <c r="G115" s="15" t="n"/>
-      <c r="I115" s="15" t="inlineStr">
-        <is>
-          <t>微台多空比位階(45日)</t>
-        </is>
-      </c>
-      <c r="J115" s="15" t="n"/>
-      <c r="K115" s="15" t="n"/>
+      <c r="I115" s="16" t="inlineStr">
+        <is>
+          <t>【CROWDING】
+散戶多單持倉占比位階(45日)</t>
+        </is>
+      </c>
+      <c r="J115" s="16" t="n"/>
+      <c r="K115" s="16" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="n">
-        <v>47.8</v>
+        <v>1.1</v>
       </c>
       <c r="B116" s="6" t="n"/>
       <c r="C116" s="6" t="n"/>
@@ -2075,11 +2101,11 @@
       </c>
       <c r="F116" s="6" t="n"/>
       <c r="G116" s="6" t="n"/>
-      <c r="I116" s="6" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="J116" s="6" t="n"/>
-      <c r="K116" s="6" t="n"/>
+      <c r="I116" s="17" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="J116" s="17" t="n"/>
+      <c r="K116" s="17" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="6" t="n"/>
@@ -2088,9 +2114,9 @@
       <c r="E117" s="6" t="n"/>
       <c r="F117" s="6" t="n"/>
       <c r="G117" s="6" t="n"/>
-      <c r="I117" s="6" t="n"/>
-      <c r="J117" s="6" t="n"/>
-      <c r="K117" s="6" t="n"/>
+      <c r="I117" s="17" t="n"/>
+      <c r="J117" s="17" t="n"/>
+      <c r="K117" s="17" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
@@ -2107,13 +2133,13 @@
       </c>
       <c r="F118" s="7" t="n"/>
       <c r="G118" s="7" t="n"/>
-      <c r="I118" s="7" t="inlineStr">
+      <c r="I118" s="18" t="inlineStr">
         <is>
           <t>近45日相對位階（同值取中間排名）= (低於本日筆數 + 同值筆數 / 2) / 樣本數 x 100。 小台＋微台等值口數；微台 5 口換算為 1 口小台等值。；目前樣本 45 筆。</t>
         </is>
       </c>
-      <c r="J118" s="7" t="n"/>
-      <c r="K118" s="7" t="n"/>
+      <c r="J118" s="18" t="n"/>
+      <c r="K118" s="18" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="n"/>
@@ -2122,23 +2148,83 @@
       <c r="E119" s="7" t="n"/>
       <c r="F119" s="7" t="n"/>
       <c r="G119" s="7" t="n"/>
-      <c r="I119" s="7" t="n"/>
-      <c r="J119" s="7" t="n"/>
-      <c r="K119" s="7" t="n"/>
+      <c r="I119" s="18" t="n"/>
+      <c r="J119" s="18" t="n"/>
+      <c r="K119" s="18" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="15" t="inlineStr">
+        <is>
+          <t>散戶空單持倉占比位階(45日)</t>
+        </is>
+      </c>
+      <c r="B121" s="15" t="n"/>
+      <c r="C121" s="15" t="n"/>
+      <c r="E121" s="15" t="inlineStr">
+        <is>
+          <t>微台多空比位階(45日)</t>
+        </is>
+      </c>
+      <c r="F121" s="15" t="n"/>
+      <c r="G121" s="15" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="16" t="inlineStr">
+      <c r="A122" s="6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="B122" s="6" t="n"/>
+      <c r="C122" s="6" t="n"/>
+      <c r="E122" s="6" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="F122" s="6" t="n"/>
+      <c r="G122" s="6" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="n"/>
+      <c r="B123" s="6" t="n"/>
+      <c r="C123" s="6" t="n"/>
+      <c r="E123" s="6" t="n"/>
+      <c r="F123" s="6" t="n"/>
+      <c r="G123" s="6" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>近45日相對位階（同值取中間排名）= (低於本日筆數 + 同值筆數 / 2) / 樣本數 x 100。 小台＋微台等值口數；微台 5 口換算為 1 口小台等值。；目前樣本 45 筆。</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="n"/>
+      <c r="C124" s="7" t="n"/>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>近45日相對位階（同值取中間排名）= (低於本日筆數 + 同值筆數 / 2) / 樣本數 x 100。 小台＋微台等值口數；微台 5 口換算為 1 口小台等值。；目前樣本 45 筆。</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="n"/>
+      <c r="G124" s="7" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="n"/>
+      <c r="B125" s="7" t="n"/>
+      <c r="C125" s="7" t="n"/>
+      <c r="E125" s="7" t="n"/>
+      <c r="F125" s="7" t="n"/>
+      <c r="G125" s="7" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="19" t="inlineStr">
         <is>
           <t>這是 2026-08-19 的盤後籌碼正式版：加權指數收 44,719.35 點、跌 589.33 點，盤中最高 45,071.34 點、最低 44,308.71 點，成交值約 8,902.70 億元；TWSE 信用交易統計已補回，融資金額餘額 5,481.90 億、較前一交易日增加 11.78 億，融券餘額 188,334 張、較前一交易日減少 16,121 張。TAIFEX 的外資(大小台)期貨未平倉依原表合併口徑 = TXF + MXF/4 + TMF/20，8/19 約為 -81,813，與結算比約 2,463、與前日增減約 1,051；主表 OP 欄位維持 BC-SC 與 BP-SP 的淨額口徑。</t>
         </is>
       </c>
     </row>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
   </sheetData>
-  <mergeCells count="158">
+  <mergeCells count="164">
     <mergeCell ref="E116:G117"/>
     <mergeCell ref="I103:K103"/>
     <mergeCell ref="E13:G13"/>
@@ -2157,6 +2243,7 @@
     <mergeCell ref="E48:G49"/>
     <mergeCell ref="A91:C91"/>
     <mergeCell ref="I104:K105"/>
+    <mergeCell ref="A128:N132"/>
     <mergeCell ref="A16:C17"/>
     <mergeCell ref="I26:K27"/>
     <mergeCell ref="I106:K107"/>
@@ -2164,6 +2251,7 @@
     <mergeCell ref="A77:C77"/>
     <mergeCell ref="E74:G75"/>
     <mergeCell ref="A83:C83"/>
+    <mergeCell ref="E121:G121"/>
     <mergeCell ref="I68:K69"/>
     <mergeCell ref="A86:C87"/>
     <mergeCell ref="I58:K59"/>
@@ -2186,8 +2274,10 @@
     <mergeCell ref="A110:C111"/>
     <mergeCell ref="A48:C49"/>
     <mergeCell ref="A97:C97"/>
+    <mergeCell ref="E122:G123"/>
     <mergeCell ref="E78:G79"/>
     <mergeCell ref="I51:K51"/>
+    <mergeCell ref="A121:C121"/>
     <mergeCell ref="A54:C55"/>
     <mergeCell ref="I72:K73"/>
     <mergeCell ref="A13:C13"/>
@@ -2212,11 +2302,11 @@
     <mergeCell ref="I25:K25"/>
     <mergeCell ref="I98:K99"/>
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A122:N126"/>
     <mergeCell ref="E19:G19"/>
     <mergeCell ref="E26:G27"/>
     <mergeCell ref="A68:C69"/>
     <mergeCell ref="E66:G67"/>
+    <mergeCell ref="E124:G125"/>
     <mergeCell ref="E106:G107"/>
     <mergeCell ref="E65:G65"/>
     <mergeCell ref="A52:C53"/>
@@ -2250,6 +2340,7 @@
     <mergeCell ref="I57:K57"/>
     <mergeCell ref="I48:K49"/>
     <mergeCell ref="A104:C105"/>
+    <mergeCell ref="A122:C123"/>
     <mergeCell ref="E80:G81"/>
     <mergeCell ref="E51:G51"/>
     <mergeCell ref="E16:G17"/>
@@ -2276,6 +2367,7 @@
     <mergeCell ref="A115:C115"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A66:C67"/>
+    <mergeCell ref="A124:C125"/>
     <mergeCell ref="I22:K23"/>
     <mergeCell ref="I28:K29"/>
     <mergeCell ref="A118:C119"/>
